--- a/CHARMS REFLEXION.xlsx
+++ b/CHARMS REFLEXION.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\CATALOGO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F836E05B-D0F0-4902-90F1-05708A411704}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03D6A21C-429A-462F-8F3B-24FB8C95497A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BAD9DA9B-3134-462C-8E65-661561964EA0}"/>
   </bookViews>
@@ -4661,7 +4661,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D86DADA-B570-46BD-B865-34E65323A1FB}">
-  <dimension ref="A1:L712"/>
+  <dimension ref="A1:L395"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="6" customWidth="1"/>
@@ -7272,7 +7272,7 @@
       <c r="J96" s="11"/>
       <c r="K96" s="11"/>
     </row>
-    <row r="97" spans="1:12" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="7">
         <v>1</v>
       </c>
@@ -7299,2466 +7299,304 @@
       <c r="J97" s="11"/>
       <c r="K97" s="11"/>
     </row>
-    <row r="98" spans="1:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H98" s="3"/>
-      <c r="L98" s="3"/>
-    </row>
-    <row r="99" spans="1:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H99" s="3"/>
-      <c r="L99" s="3"/>
-    </row>
-    <row r="100" spans="1:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H100" s="3"/>
-      <c r="L100" s="3"/>
-    </row>
-    <row r="101" spans="1:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H101" s="3"/>
-      <c r="L101" s="3"/>
-    </row>
-    <row r="102" spans="1:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H102" s="3"/>
-      <c r="L102" s="3"/>
-    </row>
-    <row r="103" spans="1:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H103" s="3"/>
-      <c r="L103" s="3"/>
-    </row>
-    <row r="104" spans="1:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H104" s="3"/>
-      <c r="L104" s="3"/>
-    </row>
-    <row r="105" spans="1:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H105" s="3"/>
-      <c r="L105" s="3"/>
-    </row>
-    <row r="106" spans="1:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H106" s="3"/>
-      <c r="L106" s="3"/>
-    </row>
-    <row r="107" spans="1:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H107" s="3"/>
-      <c r="L107" s="3"/>
-    </row>
-    <row r="108" spans="1:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H108" s="3"/>
-      <c r="L108" s="3"/>
-    </row>
-    <row r="109" spans="1:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H109" s="3"/>
-      <c r="L109" s="3"/>
-    </row>
-    <row r="110" spans="1:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H110" s="3"/>
-      <c r="L110" s="3"/>
-    </row>
-    <row r="111" spans="1:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H111" s="3"/>
-      <c r="L111" s="3"/>
-    </row>
-    <row r="112" spans="1:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H112" s="3"/>
-      <c r="L112" s="3"/>
-    </row>
-    <row r="113" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H113" s="3"/>
-      <c r="L113" s="3"/>
-    </row>
-    <row r="114" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H114" s="3"/>
-      <c r="L114" s="3"/>
-    </row>
-    <row r="115" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H115" s="3"/>
-      <c r="L115" s="3"/>
-    </row>
-    <row r="116" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H116" s="3"/>
-      <c r="L116" s="3"/>
-    </row>
-    <row r="117" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H117" s="3"/>
-      <c r="L117" s="3"/>
-    </row>
-    <row r="118" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H118" s="3"/>
-      <c r="L118" s="3"/>
-    </row>
-    <row r="119" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H119" s="3"/>
-      <c r="L119" s="3"/>
-    </row>
-    <row r="120" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H120" s="3"/>
-      <c r="L120" s="3"/>
-    </row>
-    <row r="121" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H121" s="3"/>
-      <c r="L121" s="3"/>
-    </row>
-    <row r="122" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H122" s="3"/>
-      <c r="L122" s="3"/>
-    </row>
-    <row r="123" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H123" s="3"/>
-      <c r="L123" s="3"/>
-    </row>
-    <row r="124" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H124" s="3"/>
-      <c r="L124" s="3"/>
-    </row>
-    <row r="125" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H125" s="3"/>
-      <c r="L125" s="3"/>
-    </row>
-    <row r="126" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H126" s="3"/>
-      <c r="L126" s="3"/>
-    </row>
-    <row r="127" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H127" s="3"/>
-      <c r="L127" s="3"/>
-    </row>
-    <row r="128" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H128" s="3"/>
-      <c r="L128" s="3"/>
-    </row>
-    <row r="129" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H129" s="3"/>
-      <c r="L129" s="3"/>
-    </row>
-    <row r="130" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H130" s="3"/>
-      <c r="L130" s="3"/>
-    </row>
-    <row r="131" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H131" s="3"/>
-      <c r="L131" s="3"/>
-    </row>
-    <row r="132" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H132" s="3"/>
-      <c r="L132" s="3"/>
-    </row>
-    <row r="133" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H133" s="3"/>
-      <c r="L133" s="3"/>
-    </row>
-    <row r="134" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H134" s="3"/>
-      <c r="L134" s="3"/>
-    </row>
-    <row r="135" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H135" s="3"/>
-      <c r="L135" s="3"/>
-    </row>
-    <row r="136" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H136" s="3"/>
-      <c r="L136" s="3"/>
-    </row>
-    <row r="137" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H137" s="3"/>
-      <c r="L137" s="3"/>
-    </row>
-    <row r="138" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H138" s="3"/>
-      <c r="L138" s="3"/>
-    </row>
-    <row r="139" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H139" s="3"/>
-      <c r="L139" s="3"/>
-    </row>
-    <row r="140" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H140" s="3"/>
-      <c r="L140" s="3"/>
-    </row>
-    <row r="141" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H141" s="3"/>
-      <c r="L141" s="3"/>
-    </row>
-    <row r="142" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H142" s="3"/>
-      <c r="L142" s="3"/>
-    </row>
-    <row r="143" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H143" s="3"/>
-      <c r="L143" s="3"/>
-    </row>
-    <row r="144" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H144" s="3"/>
-      <c r="L144" s="3"/>
-    </row>
-    <row r="145" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H145" s="3"/>
-      <c r="L145" s="3"/>
-    </row>
-    <row r="146" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H146" s="3"/>
-      <c r="L146" s="3"/>
-    </row>
-    <row r="147" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H147" s="3"/>
-      <c r="L147" s="3"/>
-    </row>
-    <row r="148" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H148" s="3"/>
-      <c r="L148" s="3"/>
-    </row>
-    <row r="149" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H149" s="3"/>
-      <c r="L149" s="3"/>
-    </row>
-    <row r="150" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H150" s="3"/>
-      <c r="L150" s="3"/>
-    </row>
-    <row r="151" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H151" s="3"/>
-      <c r="L151" s="3"/>
-    </row>
-    <row r="152" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H152" s="3"/>
-      <c r="L152" s="3"/>
-    </row>
-    <row r="153" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H153" s="3"/>
-      <c r="L153" s="3"/>
-    </row>
-    <row r="154" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H154" s="3"/>
-      <c r="L154" s="3"/>
-    </row>
-    <row r="155" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H155" s="3"/>
-      <c r="L155" s="3"/>
-    </row>
-    <row r="156" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H156" s="3"/>
-      <c r="L156" s="3"/>
-    </row>
-    <row r="157" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H157" s="3"/>
-      <c r="L157" s="3"/>
-    </row>
-    <row r="158" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H158" s="3"/>
-      <c r="L158" s="3"/>
-    </row>
-    <row r="159" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H159" s="3"/>
-      <c r="L159" s="3"/>
-    </row>
-    <row r="160" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H160" s="3"/>
-      <c r="L160" s="3"/>
-    </row>
-    <row r="161" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H161" s="3"/>
-      <c r="L161" s="3"/>
-    </row>
-    <row r="162" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H162" s="3"/>
-      <c r="L162" s="3"/>
-    </row>
-    <row r="163" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H163" s="3"/>
-      <c r="L163" s="3"/>
-    </row>
-    <row r="164" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H164" s="3"/>
-      <c r="L164" s="3"/>
-    </row>
-    <row r="165" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H165" s="3"/>
-      <c r="L165" s="3"/>
-    </row>
-    <row r="166" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H166" s="3"/>
-      <c r="L166" s="3"/>
-    </row>
-    <row r="167" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H167" s="3"/>
-      <c r="L167" s="3"/>
-    </row>
-    <row r="168" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H168" s="3"/>
-      <c r="L168" s="3"/>
-    </row>
-    <row r="169" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H169" s="3"/>
-      <c r="L169" s="3"/>
-    </row>
-    <row r="170" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H170" s="3"/>
-      <c r="L170" s="3"/>
-    </row>
-    <row r="171" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H171" s="3"/>
-      <c r="L171" s="3"/>
-    </row>
-    <row r="172" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H172" s="3"/>
-      <c r="L172" s="3"/>
-    </row>
-    <row r="173" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H173" s="3"/>
-      <c r="L173" s="3"/>
-    </row>
-    <row r="174" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H174" s="3"/>
-      <c r="L174" s="3"/>
-    </row>
-    <row r="175" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H175" s="3"/>
-      <c r="L175" s="3"/>
-    </row>
-    <row r="176" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H176" s="3"/>
-      <c r="L176" s="3"/>
-    </row>
-    <row r="177" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H177" s="3"/>
-      <c r="L177" s="3"/>
-    </row>
-    <row r="178" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H178" s="3"/>
-      <c r="L178" s="3"/>
-    </row>
-    <row r="179" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H179" s="3"/>
-      <c r="L179" s="3"/>
-    </row>
-    <row r="180" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H180" s="3"/>
-      <c r="L180" s="3"/>
-    </row>
-    <row r="181" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H181" s="3"/>
-      <c r="L181" s="3"/>
-    </row>
-    <row r="182" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H182" s="3"/>
-      <c r="L182" s="3"/>
-    </row>
-    <row r="183" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H183" s="3"/>
-      <c r="L183" s="3"/>
-    </row>
-    <row r="184" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H184" s="3"/>
-      <c r="L184" s="3"/>
-    </row>
-    <row r="185" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H185" s="3"/>
-      <c r="L185" s="3"/>
-    </row>
-    <row r="186" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H186" s="3"/>
-      <c r="L186" s="3"/>
-    </row>
-    <row r="187" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H187" s="3"/>
-      <c r="L187" s="3"/>
-    </row>
-    <row r="188" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H188" s="3"/>
-      <c r="L188" s="3"/>
-    </row>
-    <row r="189" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H189" s="3"/>
-      <c r="L189" s="3"/>
-    </row>
-    <row r="190" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H190" s="3"/>
-      <c r="L190" s="3"/>
-    </row>
-    <row r="191" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H191" s="3"/>
-      <c r="L191" s="3"/>
-    </row>
-    <row r="192" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H192" s="3"/>
-      <c r="L192" s="3"/>
-    </row>
-    <row r="193" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H193" s="3"/>
-      <c r="L193" s="3"/>
-    </row>
-    <row r="194" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H194" s="3"/>
-      <c r="L194" s="3"/>
-    </row>
-    <row r="195" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H195" s="3"/>
-      <c r="L195" s="3"/>
-    </row>
-    <row r="196" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H196" s="3"/>
-      <c r="L196" s="3"/>
-    </row>
-    <row r="197" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H197" s="3"/>
-      <c r="L197" s="3"/>
-    </row>
-    <row r="198" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H198" s="3"/>
-      <c r="L198" s="3"/>
-    </row>
-    <row r="199" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H199" s="3"/>
-      <c r="L199" s="3"/>
-    </row>
-    <row r="200" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H200" s="3"/>
-      <c r="L200" s="3"/>
-    </row>
-    <row r="201" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H201" s="3"/>
-      <c r="L201" s="3"/>
-    </row>
-    <row r="202" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H202" s="3"/>
-      <c r="L202" s="3"/>
-    </row>
-    <row r="203" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H203" s="3"/>
-      <c r="L203" s="3"/>
-    </row>
-    <row r="204" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H204" s="3"/>
-      <c r="L204" s="3"/>
-    </row>
-    <row r="205" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H205" s="3"/>
-      <c r="L205" s="3"/>
-    </row>
-    <row r="206" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H206" s="3"/>
-      <c r="L206" s="3"/>
-    </row>
-    <row r="207" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H207" s="3"/>
-      <c r="L207" s="3"/>
-    </row>
-    <row r="208" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H208" s="3"/>
-      <c r="L208" s="3"/>
-    </row>
-    <row r="209" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H209" s="3"/>
-      <c r="L209" s="3"/>
-    </row>
-    <row r="210" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H210" s="3"/>
-      <c r="L210" s="3"/>
-    </row>
-    <row r="211" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H211" s="3"/>
-      <c r="L211" s="3"/>
-    </row>
-    <row r="212" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H212" s="3"/>
-      <c r="L212" s="3"/>
-    </row>
-    <row r="213" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H213" s="3"/>
-      <c r="L213" s="3"/>
-    </row>
-    <row r="214" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H214" s="3"/>
-      <c r="L214" s="3"/>
-    </row>
-    <row r="215" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H215" s="3"/>
-      <c r="L215" s="3"/>
-    </row>
-    <row r="216" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H216" s="3"/>
-      <c r="L216" s="3"/>
-    </row>
-    <row r="217" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H217" s="3"/>
-      <c r="L217" s="3"/>
-    </row>
-    <row r="218" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H218" s="3"/>
-      <c r="L218" s="3"/>
-    </row>
-    <row r="219" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H219" s="3"/>
-      <c r="L219" s="3"/>
-    </row>
-    <row r="220" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H220" s="3"/>
-      <c r="L220" s="3"/>
-    </row>
-    <row r="221" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H221" s="3"/>
-      <c r="L221" s="3"/>
-    </row>
-    <row r="222" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H222" s="3"/>
-      <c r="L222" s="3"/>
-    </row>
-    <row r="223" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H223" s="3"/>
-      <c r="L223" s="3"/>
-    </row>
-    <row r="224" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H224" s="3"/>
-      <c r="L224" s="3"/>
-    </row>
-    <row r="225" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H225" s="3"/>
-      <c r="L225" s="3"/>
-    </row>
-    <row r="226" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H226" s="3"/>
-      <c r="L226" s="3"/>
-    </row>
-    <row r="227" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H227" s="3"/>
-      <c r="L227" s="3"/>
-    </row>
-    <row r="228" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H228" s="3"/>
-      <c r="L228" s="3"/>
-    </row>
-    <row r="229" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H229" s="3"/>
-      <c r="L229" s="3"/>
-    </row>
-    <row r="230" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H230" s="3"/>
-      <c r="L230" s="3"/>
-    </row>
-    <row r="231" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H231" s="3"/>
-      <c r="L231" s="3"/>
-    </row>
-    <row r="232" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H232" s="3"/>
-      <c r="L232" s="3"/>
-    </row>
-    <row r="233" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H233" s="3"/>
-      <c r="L233" s="3"/>
-    </row>
-    <row r="234" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H234" s="3"/>
-      <c r="L234" s="3"/>
-    </row>
-    <row r="235" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H235" s="3"/>
-      <c r="L235" s="3"/>
-    </row>
-    <row r="236" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H236" s="3"/>
-      <c r="L236" s="3"/>
-    </row>
-    <row r="237" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H237" s="3"/>
-      <c r="L237" s="3"/>
-    </row>
-    <row r="238" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H238" s="3"/>
-      <c r="L238" s="3"/>
-    </row>
-    <row r="239" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H239" s="3"/>
-      <c r="L239" s="3"/>
-    </row>
-    <row r="240" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H240" s="3"/>
-      <c r="L240" s="3"/>
-    </row>
-    <row r="241" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H241" s="3"/>
-      <c r="L241" s="3"/>
-    </row>
-    <row r="242" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H242" s="3"/>
-      <c r="L242" s="3"/>
-    </row>
-    <row r="243" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H243" s="3"/>
-      <c r="L243" s="3"/>
-    </row>
-    <row r="244" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H244" s="3"/>
-      <c r="L244" s="3"/>
-    </row>
-    <row r="245" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H245" s="3"/>
-      <c r="L245" s="3"/>
-    </row>
-    <row r="246" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H246" s="3"/>
-      <c r="L246" s="3"/>
-    </row>
-    <row r="247" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H247" s="3"/>
-      <c r="L247" s="3"/>
-    </row>
-    <row r="248" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H248" s="3"/>
-      <c r="L248" s="3"/>
-    </row>
-    <row r="249" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H249" s="3"/>
-      <c r="L249" s="3"/>
-    </row>
-    <row r="250" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H250" s="3"/>
-      <c r="L250" s="3"/>
-    </row>
-    <row r="251" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H251" s="3"/>
-      <c r="L251" s="3"/>
-    </row>
-    <row r="252" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H252" s="3"/>
-      <c r="L252" s="3"/>
-    </row>
-    <row r="253" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H253" s="3"/>
-      <c r="L253" s="3"/>
-    </row>
-    <row r="254" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H254" s="3"/>
-      <c r="L254" s="3"/>
-    </row>
-    <row r="255" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H255" s="3"/>
-      <c r="L255" s="3"/>
-    </row>
-    <row r="256" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H256" s="3"/>
-      <c r="L256" s="3"/>
-    </row>
-    <row r="257" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H257" s="3"/>
-      <c r="L257" s="3"/>
-    </row>
-    <row r="258" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H258" s="3"/>
-      <c r="L258" s="3"/>
-    </row>
-    <row r="259" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H259" s="3"/>
-      <c r="L259" s="3"/>
-    </row>
-    <row r="260" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H260" s="3"/>
-      <c r="L260" s="3"/>
-    </row>
-    <row r="261" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H261" s="3"/>
-      <c r="L261" s="3"/>
-    </row>
-    <row r="262" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H262" s="3"/>
-      <c r="L262" s="3"/>
-    </row>
-    <row r="263" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H263" s="3"/>
-      <c r="L263" s="3"/>
-    </row>
-    <row r="264" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H264" s="3"/>
-      <c r="L264" s="3"/>
-    </row>
-    <row r="265" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H265" s="3"/>
-      <c r="L265" s="3"/>
-    </row>
-    <row r="266" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H266" s="3"/>
-      <c r="L266" s="3"/>
-    </row>
-    <row r="267" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H267" s="3"/>
-      <c r="L267" s="3"/>
-    </row>
-    <row r="268" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H268" s="3"/>
-      <c r="L268" s="3"/>
-    </row>
-    <row r="269" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H269" s="3"/>
-      <c r="L269" s="3"/>
-    </row>
-    <row r="270" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H270" s="3"/>
-      <c r="L270" s="3"/>
-    </row>
-    <row r="271" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H271" s="3"/>
-      <c r="L271" s="3"/>
-    </row>
-    <row r="272" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H272" s="3"/>
-      <c r="L272" s="3"/>
-    </row>
-    <row r="273" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H273" s="3"/>
-      <c r="L273" s="3"/>
-    </row>
-    <row r="274" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H274" s="3"/>
-      <c r="L274" s="3"/>
-    </row>
-    <row r="275" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H275" s="3"/>
-      <c r="L275" s="3"/>
-    </row>
-    <row r="276" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H276" s="3"/>
-      <c r="L276" s="3"/>
-    </row>
-    <row r="277" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H277" s="3"/>
-      <c r="L277" s="3"/>
-    </row>
-    <row r="278" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H278" s="3"/>
-      <c r="L278" s="3"/>
-    </row>
-    <row r="279" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H279" s="3"/>
-      <c r="L279" s="3"/>
-    </row>
-    <row r="280" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H280" s="3"/>
-      <c r="L280" s="3"/>
-    </row>
-    <row r="281" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H281" s="3"/>
-      <c r="L281" s="3"/>
-    </row>
-    <row r="282" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H282" s="3"/>
-      <c r="L282" s="3"/>
-    </row>
-    <row r="283" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H283" s="3"/>
-      <c r="L283" s="3"/>
-    </row>
-    <row r="284" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H284" s="3"/>
-      <c r="L284" s="3"/>
-    </row>
-    <row r="285" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H285" s="3"/>
-      <c r="L285" s="3"/>
-    </row>
-    <row r="286" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H286" s="3"/>
-      <c r="L286" s="3"/>
-    </row>
-    <row r="287" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H287" s="3"/>
-      <c r="L287" s="3"/>
-    </row>
-    <row r="288" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H288" s="3"/>
-      <c r="L288" s="3"/>
-    </row>
-    <row r="289" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H289" s="3"/>
-      <c r="L289" s="3"/>
-    </row>
-    <row r="290" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H290" s="3"/>
-      <c r="L290" s="3"/>
-    </row>
-    <row r="291" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H291" s="3"/>
-      <c r="L291" s="3"/>
-    </row>
-    <row r="292" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H292" s="3"/>
-      <c r="L292" s="3"/>
-    </row>
-    <row r="293" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H293" s="3"/>
-      <c r="L293" s="3"/>
-    </row>
-    <row r="294" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H294" s="3"/>
-      <c r="L294" s="3"/>
-    </row>
-    <row r="295" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H295" s="3"/>
-      <c r="L295" s="3"/>
-    </row>
-    <row r="296" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H296" s="3"/>
-      <c r="L296" s="3"/>
-    </row>
-    <row r="297" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H297" s="3"/>
-      <c r="L297" s="3"/>
-    </row>
-    <row r="298" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H298" s="3"/>
-      <c r="L298" s="3"/>
-    </row>
-    <row r="299" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H299" s="3"/>
-      <c r="L299" s="3"/>
-    </row>
-    <row r="300" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H300" s="3"/>
-      <c r="L300" s="3"/>
-    </row>
-    <row r="301" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H301" s="3"/>
-      <c r="L301" s="3"/>
-    </row>
-    <row r="302" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H302" s="3"/>
-      <c r="L302" s="3"/>
-    </row>
-    <row r="303" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H303" s="3"/>
-      <c r="L303" s="3"/>
-    </row>
-    <row r="304" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H304" s="3"/>
-      <c r="L304" s="3"/>
-    </row>
-    <row r="305" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H305" s="3"/>
-      <c r="L305" s="3"/>
-    </row>
-    <row r="306" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H306" s="3"/>
-      <c r="L306" s="3"/>
-    </row>
-    <row r="307" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H307" s="3"/>
-      <c r="L307" s="3"/>
-    </row>
-    <row r="308" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H308" s="3"/>
-      <c r="L308" s="3"/>
-    </row>
-    <row r="309" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H309" s="3"/>
-      <c r="L309" s="3"/>
-    </row>
-    <row r="310" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H310" s="3"/>
-      <c r="L310" s="3"/>
-    </row>
-    <row r="311" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H311" s="3"/>
-      <c r="L311" s="3"/>
-    </row>
-    <row r="312" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H312" s="3"/>
-      <c r="L312" s="3"/>
-    </row>
-    <row r="313" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H313" s="3"/>
-      <c r="L313" s="3"/>
-    </row>
-    <row r="314" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H314" s="3"/>
-      <c r="L314" s="3"/>
-    </row>
-    <row r="315" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H315" s="3"/>
-      <c r="L315" s="3"/>
-    </row>
-    <row r="316" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H316" s="3"/>
-      <c r="L316" s="3"/>
-    </row>
-    <row r="317" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H317" s="3"/>
-      <c r="L317" s="3"/>
-    </row>
-    <row r="318" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H318" s="3"/>
-      <c r="L318" s="3"/>
-    </row>
-    <row r="319" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H319" s="3"/>
-      <c r="L319" s="3"/>
-    </row>
-    <row r="320" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H320" s="3"/>
-      <c r="L320" s="3"/>
-    </row>
-    <row r="321" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H321" s="3"/>
-      <c r="L321" s="3"/>
-    </row>
-    <row r="322" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H322" s="3"/>
-      <c r="L322" s="3"/>
-    </row>
-    <row r="323" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H323" s="3"/>
-      <c r="L323" s="3"/>
-    </row>
-    <row r="324" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H324" s="3"/>
-      <c r="L324" s="3"/>
-    </row>
-    <row r="325" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H325" s="3"/>
-      <c r="L325" s="3"/>
-    </row>
-    <row r="326" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H326" s="3"/>
-      <c r="L326" s="3"/>
-    </row>
-    <row r="327" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H327" s="3"/>
-      <c r="L327" s="3"/>
-    </row>
-    <row r="328" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H328" s="3"/>
-      <c r="L328" s="3"/>
-    </row>
-    <row r="329" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H329" s="3"/>
-      <c r="L329" s="3"/>
-    </row>
-    <row r="330" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H330" s="3"/>
-      <c r="L330" s="3"/>
-    </row>
-    <row r="331" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H331" s="3"/>
-      <c r="L331" s="3"/>
-    </row>
-    <row r="332" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H332" s="3"/>
-      <c r="L332" s="3"/>
-    </row>
-    <row r="333" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H333" s="3"/>
-      <c r="L333" s="3"/>
-    </row>
-    <row r="334" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H334" s="3"/>
-      <c r="L334" s="3"/>
-    </row>
-    <row r="335" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H335" s="3"/>
-      <c r="L335" s="3"/>
-    </row>
-    <row r="336" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H336" s="3"/>
-      <c r="L336" s="3"/>
-    </row>
-    <row r="337" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H337" s="3"/>
-      <c r="L337" s="3"/>
-    </row>
-    <row r="338" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H338" s="3"/>
-      <c r="L338" s="3"/>
-    </row>
-    <row r="339" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H339" s="3"/>
-      <c r="L339" s="3"/>
-    </row>
-    <row r="340" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H340" s="3"/>
-      <c r="L340" s="3"/>
-    </row>
-    <row r="341" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H341" s="3"/>
-      <c r="L341" s="3"/>
-    </row>
-    <row r="342" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H342" s="3"/>
-      <c r="L342" s="3"/>
-    </row>
-    <row r="343" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H343" s="3"/>
-      <c r="L343" s="3"/>
-    </row>
-    <row r="344" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H344" s="3"/>
-      <c r="L344" s="3"/>
-    </row>
-    <row r="345" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H345" s="3"/>
-      <c r="L345" s="3"/>
-    </row>
-    <row r="346" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H346" s="3"/>
-      <c r="L346" s="3"/>
-    </row>
-    <row r="347" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H347" s="3"/>
-      <c r="L347" s="3"/>
-    </row>
-    <row r="348" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H348" s="3"/>
-      <c r="L348" s="3"/>
-    </row>
-    <row r="349" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H349" s="3"/>
-      <c r="L349" s="3"/>
-    </row>
-    <row r="350" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H350" s="3"/>
-      <c r="L350" s="3"/>
-    </row>
-    <row r="351" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H351" s="3"/>
-      <c r="L351" s="3"/>
-    </row>
-    <row r="352" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H352" s="3"/>
-      <c r="L352" s="3"/>
-    </row>
-    <row r="353" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H353" s="3"/>
-      <c r="L353" s="3"/>
-    </row>
-    <row r="354" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H354" s="3"/>
-      <c r="L354" s="3"/>
-    </row>
-    <row r="355" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H355" s="3"/>
-      <c r="L355" s="3"/>
-    </row>
-    <row r="356" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H356" s="3"/>
-      <c r="L356" s="3"/>
-    </row>
-    <row r="357" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H357" s="3"/>
-      <c r="L357" s="3"/>
-    </row>
-    <row r="358" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H358" s="3"/>
-      <c r="L358" s="3"/>
-    </row>
-    <row r="359" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H359" s="3"/>
-      <c r="L359" s="3"/>
-    </row>
-    <row r="360" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H360" s="3"/>
-      <c r="L360" s="3"/>
-    </row>
-    <row r="361" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H361" s="3"/>
-      <c r="L361" s="3"/>
-    </row>
-    <row r="362" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H362" s="3"/>
-      <c r="L362" s="3"/>
-    </row>
-    <row r="363" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H363" s="3"/>
-      <c r="L363" s="3"/>
-    </row>
-    <row r="364" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H364" s="3"/>
-      <c r="L364" s="3"/>
-    </row>
-    <row r="365" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H365" s="3"/>
-      <c r="L365" s="3"/>
-    </row>
-    <row r="366" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H366" s="3"/>
-      <c r="L366" s="3"/>
-    </row>
-    <row r="367" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H367" s="3"/>
-      <c r="L367" s="3"/>
-    </row>
-    <row r="368" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H368" s="3"/>
-      <c r="L368" s="3"/>
-    </row>
-    <row r="369" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H369" s="3"/>
-      <c r="L369" s="3"/>
-    </row>
-    <row r="370" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H370" s="3"/>
-      <c r="L370" s="3"/>
-    </row>
-    <row r="371" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H371" s="3"/>
-      <c r="L371" s="3"/>
-    </row>
-    <row r="372" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H372" s="3"/>
-      <c r="L372" s="3"/>
-    </row>
-    <row r="373" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H373" s="3"/>
-      <c r="L373" s="3"/>
-    </row>
-    <row r="374" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H374" s="3"/>
-      <c r="L374" s="3"/>
-    </row>
-    <row r="375" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H375" s="3"/>
-      <c r="L375" s="3"/>
-    </row>
-    <row r="376" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H376" s="3"/>
-      <c r="L376" s="3"/>
-    </row>
-    <row r="377" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H377" s="3"/>
-      <c r="L377" s="3"/>
-    </row>
-    <row r="378" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H378" s="3"/>
-      <c r="L378" s="3"/>
-    </row>
-    <row r="379" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H379" s="3"/>
-      <c r="L379" s="3"/>
-    </row>
-    <row r="380" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H380" s="3"/>
-      <c r="L380" s="3"/>
-    </row>
-    <row r="381" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H381" s="3"/>
-      <c r="L381" s="3"/>
-    </row>
-    <row r="382" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H382" s="3"/>
-      <c r="L382" s="3"/>
-    </row>
-    <row r="383" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H383" s="3"/>
-      <c r="L383" s="3"/>
-    </row>
-    <row r="384" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H384" s="3"/>
-      <c r="L384" s="3"/>
-    </row>
-    <row r="385" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H385" s="3"/>
-      <c r="L385" s="3"/>
-    </row>
-    <row r="386" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H386" s="3"/>
-      <c r="L386" s="3"/>
-    </row>
-    <row r="387" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H387" s="3"/>
-      <c r="L387" s="3"/>
-    </row>
-    <row r="388" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H388" s="3"/>
-      <c r="L388" s="3"/>
-    </row>
-    <row r="389" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H389" s="3"/>
-      <c r="L389" s="3"/>
-    </row>
-    <row r="390" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H390" s="3"/>
-      <c r="L390" s="3"/>
-    </row>
-    <row r="391" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H391" s="3"/>
-      <c r="L391" s="3"/>
-    </row>
-    <row r="392" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H392" s="3"/>
-      <c r="L392" s="3"/>
-    </row>
-    <row r="393" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H393" s="3"/>
-      <c r="L393" s="3"/>
-    </row>
-    <row r="394" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H394" s="3"/>
-      <c r="L394" s="3"/>
-    </row>
-    <row r="395" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H395" s="3"/>
-      <c r="L395" s="3"/>
-    </row>
-    <row r="396" spans="8:12" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H396" s="3"/>
-      <c r="L396" s="3"/>
-    </row>
-    <row r="397" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H397" s="3"/>
-      <c r="L397" s="3"/>
-    </row>
-    <row r="398" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H398" s="3"/>
-      <c r="L398" s="3"/>
-    </row>
-    <row r="399" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H399" s="3"/>
-      <c r="L399" s="3"/>
-    </row>
-    <row r="400" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H400" s="3"/>
-      <c r="L400" s="3"/>
-    </row>
-    <row r="401" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H401" s="3"/>
-      <c r="L401" s="3"/>
-    </row>
-    <row r="402" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H402" s="3"/>
-      <c r="L402" s="3"/>
-    </row>
-    <row r="403" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H403" s="3"/>
-      <c r="L403" s="3"/>
-    </row>
-    <row r="404" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H404" s="3"/>
-      <c r="L404" s="3"/>
-    </row>
-    <row r="405" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H405" s="3"/>
-      <c r="L405" s="3"/>
-    </row>
-    <row r="406" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H406" s="3"/>
-      <c r="L406" s="3"/>
-    </row>
-    <row r="407" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H407" s="3"/>
-      <c r="L407" s="3"/>
-    </row>
-    <row r="408" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H408" s="3"/>
-      <c r="L408" s="3"/>
-    </row>
-    <row r="409" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H409" s="3"/>
-      <c r="L409" s="3"/>
-    </row>
-    <row r="410" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H410" s="3"/>
-      <c r="L410" s="3"/>
-    </row>
-    <row r="411" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H411" s="3"/>
-      <c r="L411" s="3"/>
-    </row>
-    <row r="412" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H412" s="3"/>
-      <c r="L412" s="3"/>
-    </row>
-    <row r="413" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H413" s="3"/>
-      <c r="L413" s="3"/>
-    </row>
-    <row r="414" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H414" s="3"/>
-      <c r="L414" s="3"/>
-    </row>
-    <row r="415" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H415" s="3"/>
-      <c r="L415" s="3"/>
-    </row>
-    <row r="416" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H416" s="3"/>
-      <c r="L416" s="3"/>
-    </row>
-    <row r="417" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H417" s="3"/>
-      <c r="L417" s="3"/>
-    </row>
-    <row r="418" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H418" s="3"/>
-      <c r="L418" s="3"/>
-    </row>
-    <row r="419" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H419" s="3"/>
-      <c r="L419" s="3"/>
-    </row>
-    <row r="420" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H420" s="3"/>
-      <c r="L420" s="3"/>
-    </row>
-    <row r="421" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H421" s="3"/>
-      <c r="L421" s="3"/>
-    </row>
-    <row r="422" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H422" s="3"/>
-      <c r="L422" s="3"/>
-    </row>
-    <row r="423" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H423" s="3"/>
-      <c r="L423" s="3"/>
-    </row>
-    <row r="424" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H424" s="3"/>
-      <c r="L424" s="3"/>
-    </row>
-    <row r="425" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H425" s="3"/>
-      <c r="L425" s="3"/>
-    </row>
-    <row r="426" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H426" s="3"/>
-      <c r="L426" s="3"/>
-    </row>
-    <row r="427" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H427" s="3"/>
-      <c r="L427" s="3"/>
-    </row>
-    <row r="428" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H428" s="3"/>
-      <c r="L428" s="3"/>
-    </row>
-    <row r="429" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H429" s="3"/>
-      <c r="L429" s="3"/>
-    </row>
-    <row r="430" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H430" s="3"/>
-      <c r="L430" s="3"/>
-    </row>
-    <row r="431" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H431" s="3"/>
-      <c r="L431" s="3"/>
-    </row>
-    <row r="432" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H432" s="3"/>
-      <c r="L432" s="3"/>
-    </row>
-    <row r="433" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H433" s="3"/>
-      <c r="L433" s="3"/>
-    </row>
-    <row r="434" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H434" s="3"/>
-      <c r="L434" s="3"/>
-    </row>
-    <row r="435" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H435" s="3"/>
-      <c r="L435" s="3"/>
-    </row>
-    <row r="436" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H436" s="3"/>
-      <c r="L436" s="3"/>
-    </row>
-    <row r="437" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H437" s="3"/>
-      <c r="L437" s="3"/>
-    </row>
-    <row r="438" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H438" s="3"/>
-      <c r="L438" s="3"/>
-    </row>
-    <row r="439" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H439" s="3"/>
-      <c r="L439" s="3"/>
-    </row>
-    <row r="440" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H440" s="3"/>
-      <c r="L440" s="3"/>
-    </row>
-    <row r="441" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H441" s="3"/>
-      <c r="L441" s="3"/>
-    </row>
-    <row r="442" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H442" s="3"/>
-      <c r="L442" s="3"/>
-    </row>
-    <row r="443" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H443" s="3"/>
-      <c r="L443" s="3"/>
-    </row>
-    <row r="444" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H444" s="3"/>
-      <c r="L444" s="3"/>
-    </row>
-    <row r="445" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H445" s="3"/>
-      <c r="L445" s="3"/>
-    </row>
-    <row r="446" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H446" s="3"/>
-      <c r="L446" s="3"/>
-    </row>
-    <row r="447" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H447" s="3"/>
-      <c r="L447" s="3"/>
-    </row>
-    <row r="448" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H448" s="3"/>
-      <c r="L448" s="3"/>
-    </row>
-    <row r="449" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H449" s="3"/>
-      <c r="L449" s="3"/>
-    </row>
-    <row r="450" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H450" s="3"/>
-      <c r="L450" s="3"/>
-    </row>
-    <row r="451" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H451" s="3"/>
-      <c r="L451" s="3"/>
-    </row>
-    <row r="452" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H452" s="3"/>
-      <c r="L452" s="3"/>
-    </row>
-    <row r="453" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H453" s="3"/>
-      <c r="L453" s="3"/>
-    </row>
-    <row r="454" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H454" s="3"/>
-      <c r="L454" s="3"/>
-    </row>
-    <row r="455" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H455" s="3"/>
-      <c r="L455" s="3"/>
-    </row>
-    <row r="456" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H456" s="3"/>
-      <c r="L456" s="3"/>
-    </row>
-    <row r="457" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H457" s="3"/>
-      <c r="L457" s="3"/>
-    </row>
-    <row r="458" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H458" s="3"/>
-      <c r="L458" s="3"/>
-    </row>
-    <row r="459" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H459" s="3"/>
-      <c r="L459" s="3"/>
-    </row>
-    <row r="460" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H460" s="3"/>
-      <c r="L460" s="3"/>
-    </row>
-    <row r="461" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H461" s="3"/>
-      <c r="L461" s="3"/>
-    </row>
-    <row r="462" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H462" s="3"/>
-      <c r="L462" s="3"/>
-    </row>
-    <row r="463" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H463" s="3"/>
-      <c r="L463" s="3"/>
-    </row>
-    <row r="464" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H464" s="3"/>
-      <c r="L464" s="3"/>
-    </row>
-    <row r="465" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H465" s="3"/>
-      <c r="L465" s="3"/>
-    </row>
-    <row r="466" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H466" s="3"/>
-      <c r="L466" s="3"/>
-    </row>
-    <row r="467" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H467" s="3"/>
-      <c r="L467" s="3"/>
-    </row>
-    <row r="468" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H468" s="3"/>
-      <c r="L468" s="3"/>
-    </row>
-    <row r="469" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H469" s="3"/>
-      <c r="L469" s="3"/>
-    </row>
-    <row r="470" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H470" s="3"/>
-      <c r="L470" s="3"/>
-    </row>
-    <row r="471" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H471" s="3"/>
-      <c r="L471" s="3"/>
-    </row>
-    <row r="472" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H472" s="3"/>
-      <c r="L472" s="3"/>
-    </row>
-    <row r="473" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H473" s="3"/>
-      <c r="L473" s="3"/>
-    </row>
-    <row r="474" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H474" s="3"/>
-      <c r="L474" s="3"/>
-    </row>
-    <row r="475" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H475" s="3"/>
-      <c r="L475" s="3"/>
-    </row>
-    <row r="476" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H476" s="3"/>
-      <c r="L476" s="3"/>
-    </row>
-    <row r="477" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H477" s="3"/>
-      <c r="L477" s="3"/>
-    </row>
-    <row r="478" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H478" s="3"/>
-      <c r="L478" s="3"/>
-    </row>
-    <row r="479" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H479" s="3"/>
-      <c r="L479" s="3"/>
-    </row>
-    <row r="480" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H480" s="3"/>
-      <c r="L480" s="3"/>
-    </row>
-    <row r="481" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H481" s="3"/>
-      <c r="L481" s="3"/>
-    </row>
-    <row r="482" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H482" s="3"/>
-      <c r="L482" s="3"/>
-    </row>
-    <row r="483" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H483" s="3"/>
-      <c r="L483" s="3"/>
-    </row>
-    <row r="484" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H484" s="3"/>
-      <c r="L484" s="3"/>
-    </row>
-    <row r="485" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H485" s="3"/>
-      <c r="L485" s="3"/>
-    </row>
-    <row r="486" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H486" s="3"/>
-      <c r="L486" s="3"/>
-    </row>
-    <row r="487" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H487" s="3"/>
-      <c r="L487" s="3"/>
-    </row>
-    <row r="488" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H488" s="3"/>
-      <c r="L488" s="3"/>
-    </row>
-    <row r="489" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H489" s="3"/>
-      <c r="L489" s="3"/>
-    </row>
-    <row r="490" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H490" s="3"/>
-      <c r="L490" s="3"/>
-    </row>
-    <row r="491" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H491" s="3"/>
-      <c r="L491" s="3"/>
-    </row>
-    <row r="492" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H492" s="3"/>
-      <c r="L492" s="3"/>
-    </row>
-    <row r="493" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H493" s="3"/>
-      <c r="L493" s="3"/>
-    </row>
-    <row r="494" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H494" s="3"/>
-      <c r="L494" s="3"/>
-    </row>
-    <row r="495" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H495" s="3"/>
-      <c r="L495" s="3"/>
-    </row>
-    <row r="496" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H496" s="3"/>
-      <c r="L496" s="3"/>
-    </row>
-    <row r="497" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H497" s="3"/>
-      <c r="L497" s="3"/>
-    </row>
-    <row r="498" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H498" s="3"/>
-      <c r="L498" s="3"/>
-    </row>
-    <row r="499" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H499" s="3"/>
-      <c r="L499" s="3"/>
-    </row>
-    <row r="500" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H500" s="3"/>
-      <c r="L500" s="3"/>
-    </row>
-    <row r="501" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H501" s="3"/>
-      <c r="L501" s="3"/>
-    </row>
-    <row r="502" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H502" s="3"/>
-      <c r="L502" s="3"/>
-    </row>
-    <row r="503" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H503" s="3"/>
-      <c r="L503" s="3"/>
-    </row>
-    <row r="504" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H504" s="3"/>
-      <c r="L504" s="3"/>
-    </row>
-    <row r="505" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H505" s="3"/>
-      <c r="L505" s="3"/>
-    </row>
-    <row r="506" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H506" s="3"/>
-      <c r="L506" s="3"/>
-    </row>
-    <row r="507" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H507" s="3"/>
-      <c r="L507" s="3"/>
-    </row>
-    <row r="508" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H508" s="3"/>
-      <c r="L508" s="3"/>
-    </row>
-    <row r="509" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H509" s="3"/>
-      <c r="L509" s="3"/>
-    </row>
-    <row r="510" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H510" s="3"/>
-      <c r="L510" s="3"/>
-    </row>
-    <row r="511" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H511" s="3"/>
-      <c r="L511" s="3"/>
-    </row>
-    <row r="512" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H512" s="3"/>
-      <c r="L512" s="3"/>
-    </row>
-    <row r="513" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H513" s="3"/>
-      <c r="L513" s="3"/>
-    </row>
-    <row r="514" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H514" s="3"/>
-      <c r="L514" s="3"/>
-    </row>
-    <row r="515" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H515" s="3"/>
-      <c r="L515" s="3"/>
-    </row>
-    <row r="516" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H516" s="3"/>
-      <c r="L516" s="3"/>
-    </row>
-    <row r="517" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H517" s="3"/>
-      <c r="L517" s="3"/>
-    </row>
-    <row r="518" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H518" s="3"/>
-      <c r="L518" s="3"/>
-    </row>
-    <row r="519" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H519" s="3"/>
-      <c r="L519" s="3"/>
-    </row>
-    <row r="520" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H520" s="3"/>
-      <c r="L520" s="3"/>
-    </row>
-    <row r="521" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H521" s="3"/>
-      <c r="L521" s="3"/>
-    </row>
-    <row r="522" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H522" s="3"/>
-      <c r="L522" s="3"/>
-    </row>
-    <row r="523" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H523" s="3"/>
-      <c r="L523" s="3"/>
-    </row>
-    <row r="524" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H524" s="3"/>
-      <c r="L524" s="3"/>
-    </row>
-    <row r="525" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H525" s="3"/>
-      <c r="L525" s="3"/>
-    </row>
-    <row r="526" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H526" s="3"/>
-      <c r="L526" s="3"/>
-    </row>
-    <row r="527" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H527" s="3"/>
-      <c r="L527" s="3"/>
-    </row>
-    <row r="528" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H528" s="3"/>
-      <c r="L528" s="3"/>
-    </row>
-    <row r="529" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H529" s="3"/>
-      <c r="L529" s="3"/>
-    </row>
-    <row r="530" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H530" s="3"/>
-      <c r="L530" s="3"/>
-    </row>
-    <row r="531" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H531" s="3"/>
-      <c r="L531" s="3"/>
-    </row>
-    <row r="532" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H532" s="3"/>
-      <c r="L532" s="3"/>
-    </row>
-    <row r="533" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H533" s="3"/>
-      <c r="L533" s="3"/>
-    </row>
-    <row r="534" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H534" s="3"/>
-      <c r="L534" s="3"/>
-    </row>
-    <row r="535" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H535" s="3"/>
-      <c r="L535" s="3"/>
-    </row>
-    <row r="536" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H536" s="3"/>
-      <c r="L536" s="3"/>
-    </row>
-    <row r="537" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H537" s="3"/>
-      <c r="L537" s="3"/>
-    </row>
-    <row r="538" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H538" s="3"/>
-      <c r="L538" s="3"/>
-    </row>
-    <row r="539" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H539" s="3"/>
-      <c r="L539" s="3"/>
-    </row>
-    <row r="540" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H540" s="3"/>
-      <c r="L540" s="3"/>
-    </row>
-    <row r="541" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H541" s="3"/>
-      <c r="L541" s="3"/>
-    </row>
-    <row r="542" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H542" s="3"/>
-      <c r="L542" s="3"/>
-    </row>
-    <row r="543" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H543" s="3"/>
-      <c r="L543" s="3"/>
-    </row>
-    <row r="544" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H544" s="3"/>
-      <c r="L544" s="3"/>
-    </row>
-    <row r="545" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H545" s="3"/>
-      <c r="L545" s="3"/>
-    </row>
-    <row r="546" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H546" s="3"/>
-      <c r="L546" s="3"/>
-    </row>
-    <row r="547" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H547" s="3"/>
-      <c r="L547" s="3"/>
-    </row>
-    <row r="548" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H548" s="3"/>
-      <c r="L548" s="3"/>
-    </row>
-    <row r="549" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H549" s="3"/>
-      <c r="L549" s="3"/>
-    </row>
-    <row r="550" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H550" s="3"/>
-      <c r="L550" s="3"/>
-    </row>
-    <row r="551" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H551" s="3"/>
-      <c r="L551" s="3"/>
-    </row>
-    <row r="552" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H552" s="3"/>
-      <c r="L552" s="3"/>
-    </row>
-    <row r="553" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H553" s="3"/>
-      <c r="L553" s="3"/>
-    </row>
-    <row r="554" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H554" s="3"/>
-      <c r="L554" s="3"/>
-    </row>
-    <row r="555" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H555" s="3"/>
-      <c r="L555" s="3"/>
-    </row>
-    <row r="556" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H556" s="3"/>
-      <c r="L556" s="3"/>
-    </row>
-    <row r="557" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H557" s="3"/>
-      <c r="L557" s="3"/>
-    </row>
-    <row r="558" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H558" s="3"/>
-      <c r="L558" s="3"/>
-    </row>
-    <row r="559" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H559" s="3"/>
-      <c r="L559" s="3"/>
-    </row>
-    <row r="560" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H560" s="3"/>
-      <c r="L560" s="3"/>
-    </row>
-    <row r="561" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H561" s="3"/>
-      <c r="L561" s="3"/>
-    </row>
-    <row r="562" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H562" s="3"/>
-      <c r="L562" s="3"/>
-    </row>
-    <row r="563" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H563" s="3"/>
-      <c r="L563" s="3"/>
-    </row>
-    <row r="564" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H564" s="3"/>
-      <c r="L564" s="3"/>
-    </row>
-    <row r="565" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H565" s="3"/>
-      <c r="L565" s="3"/>
-    </row>
-    <row r="566" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H566" s="3"/>
-      <c r="L566" s="3"/>
-    </row>
-    <row r="567" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H567" s="3"/>
-      <c r="L567" s="3"/>
-    </row>
-    <row r="568" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H568" s="3"/>
-      <c r="L568" s="3"/>
-    </row>
-    <row r="569" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H569" s="3"/>
-      <c r="L569" s="3"/>
-    </row>
-    <row r="570" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H570" s="3"/>
-      <c r="L570" s="3"/>
-    </row>
-    <row r="571" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H571" s="3"/>
-      <c r="L571" s="3"/>
-    </row>
-    <row r="572" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H572" s="3"/>
-      <c r="L572" s="3"/>
-    </row>
-    <row r="573" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H573" s="3"/>
-      <c r="L573" s="3"/>
-    </row>
-    <row r="574" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H574" s="3"/>
-      <c r="L574" s="3"/>
-    </row>
-    <row r="575" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H575" s="3"/>
-      <c r="L575" s="3"/>
-    </row>
-    <row r="576" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H576" s="3"/>
-      <c r="L576" s="3"/>
-    </row>
-    <row r="577" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H577" s="3"/>
-      <c r="L577" s="3"/>
-    </row>
-    <row r="578" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H578" s="3"/>
-      <c r="L578" s="3"/>
-    </row>
-    <row r="579" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H579" s="3"/>
-      <c r="L579" s="3"/>
-    </row>
-    <row r="580" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H580" s="3"/>
-      <c r="L580" s="3"/>
-    </row>
-    <row r="581" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H581" s="3"/>
-      <c r="L581" s="3"/>
-    </row>
-    <row r="582" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H582" s="3"/>
-      <c r="L582" s="3"/>
-    </row>
-    <row r="583" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H583" s="3"/>
-      <c r="L583" s="3"/>
-    </row>
-    <row r="584" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H584" s="3"/>
-      <c r="L584" s="3"/>
-    </row>
-    <row r="585" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H585" s="3"/>
-      <c r="L585" s="3"/>
-    </row>
-    <row r="586" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H586" s="3"/>
-      <c r="L586" s="3"/>
-    </row>
-    <row r="587" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H587" s="3"/>
-      <c r="L587" s="3"/>
-    </row>
-    <row r="588" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H588" s="3"/>
-      <c r="L588" s="3"/>
-    </row>
-    <row r="589" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H589" s="3"/>
-      <c r="L589" s="3"/>
-    </row>
-    <row r="590" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H590" s="3"/>
-      <c r="L590" s="3"/>
-    </row>
-    <row r="591" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H591" s="3"/>
-      <c r="L591" s="3"/>
-    </row>
-    <row r="592" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H592" s="3"/>
-      <c r="L592" s="3"/>
-    </row>
-    <row r="593" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H593" s="3"/>
-      <c r="L593" s="3"/>
-    </row>
-    <row r="594" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H594" s="3"/>
-      <c r="L594" s="3"/>
-    </row>
-    <row r="595" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H595" s="3"/>
-      <c r="L595" s="3"/>
-    </row>
-    <row r="596" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H596" s="3"/>
-      <c r="L596" s="3"/>
-    </row>
-    <row r="597" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H597" s="3"/>
-      <c r="L597" s="3"/>
-    </row>
-    <row r="598" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H598" s="3"/>
-      <c r="L598" s="3"/>
-    </row>
-    <row r="599" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H599" s="3"/>
-      <c r="L599" s="3"/>
-    </row>
-    <row r="600" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H600" s="3"/>
-      <c r="L600" s="3"/>
-    </row>
-    <row r="601" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H601" s="3"/>
-      <c r="L601" s="3"/>
-    </row>
-    <row r="602" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H602" s="3"/>
-      <c r="L602" s="3"/>
-    </row>
-    <row r="603" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H603" s="3"/>
-      <c r="L603" s="3"/>
-    </row>
-    <row r="604" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H604" s="3"/>
-      <c r="L604" s="3"/>
-    </row>
-    <row r="605" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H605" s="3"/>
-      <c r="L605" s="3"/>
-    </row>
-    <row r="606" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H606" s="3"/>
-      <c r="L606" s="3"/>
-    </row>
-    <row r="607" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H607" s="3"/>
-      <c r="L607" s="3"/>
-    </row>
-    <row r="608" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H608" s="3"/>
-      <c r="L608" s="3"/>
-    </row>
-    <row r="609" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H609" s="3"/>
-      <c r="L609" s="3"/>
-    </row>
-    <row r="610" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H610" s="3"/>
-      <c r="L610" s="3"/>
-    </row>
-    <row r="611" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H611" s="3"/>
-      <c r="L611" s="3"/>
-    </row>
-    <row r="612" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H612" s="3"/>
-      <c r="L612" s="3"/>
-    </row>
-    <row r="613" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H613" s="3"/>
-      <c r="L613" s="3"/>
-    </row>
-    <row r="614" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H614" s="3"/>
-      <c r="L614" s="3"/>
-    </row>
-    <row r="615" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H615" s="3"/>
-      <c r="L615" s="3"/>
-    </row>
-    <row r="616" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H616" s="3"/>
-      <c r="L616" s="3"/>
-    </row>
-    <row r="617" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H617" s="3"/>
-      <c r="L617" s="3"/>
-    </row>
-    <row r="618" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H618" s="3"/>
-      <c r="L618" s="3"/>
-    </row>
-    <row r="619" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H619" s="3"/>
-      <c r="L619" s="3"/>
-    </row>
-    <row r="620" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H620" s="3"/>
-      <c r="L620" s="3"/>
-    </row>
-    <row r="621" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H621" s="3"/>
-      <c r="L621" s="3"/>
-    </row>
-    <row r="622" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H622" s="3"/>
-      <c r="L622" s="3"/>
-    </row>
-    <row r="623" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H623" s="3"/>
-      <c r="L623" s="3"/>
-    </row>
-    <row r="624" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H624" s="3"/>
-      <c r="L624" s="3"/>
-    </row>
-    <row r="625" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H625" s="3"/>
-      <c r="L625" s="3"/>
-    </row>
-    <row r="626" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H626" s="3"/>
-      <c r="L626" s="3"/>
-    </row>
-    <row r="627" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H627" s="3"/>
-      <c r="L627" s="3"/>
-    </row>
-    <row r="628" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H628" s="3"/>
-      <c r="L628" s="3"/>
-    </row>
-    <row r="629" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H629" s="3"/>
-      <c r="L629" s="3"/>
-    </row>
-    <row r="630" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H630" s="3"/>
-      <c r="L630" s="3"/>
-    </row>
-    <row r="631" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H631" s="3"/>
-      <c r="L631" s="3"/>
-    </row>
-    <row r="632" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H632" s="3"/>
-      <c r="L632" s="3"/>
-    </row>
-    <row r="633" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H633" s="3"/>
-      <c r="L633" s="3"/>
-    </row>
-    <row r="634" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H634" s="3"/>
-      <c r="L634" s="3"/>
-    </row>
-    <row r="635" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H635" s="3"/>
-      <c r="L635" s="3"/>
-    </row>
-    <row r="636" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H636" s="3"/>
-      <c r="L636" s="3"/>
-    </row>
-    <row r="637" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H637" s="3"/>
-      <c r="L637" s="3"/>
-    </row>
-    <row r="638" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H638" s="3"/>
-      <c r="L638" s="3"/>
-    </row>
-    <row r="639" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H639" s="3"/>
-      <c r="L639" s="3"/>
-    </row>
-    <row r="640" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H640" s="3"/>
-      <c r="L640" s="3"/>
-    </row>
-    <row r="641" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H641" s="3"/>
-      <c r="L641" s="3"/>
-    </row>
-    <row r="642" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H642" s="3"/>
-      <c r="L642" s="3"/>
-    </row>
-    <row r="643" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H643" s="3"/>
-      <c r="L643" s="3"/>
-    </row>
-    <row r="644" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H644" s="3"/>
-      <c r="L644" s="3"/>
-    </row>
-    <row r="645" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H645" s="3"/>
-      <c r="L645" s="3"/>
-    </row>
-    <row r="646" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H646" s="3"/>
-      <c r="L646" s="3"/>
-    </row>
-    <row r="647" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H647" s="3"/>
-      <c r="L647" s="3"/>
-    </row>
-    <row r="648" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H648" s="3"/>
-      <c r="L648" s="3"/>
-    </row>
-    <row r="649" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H649" s="3"/>
-      <c r="L649" s="3"/>
-    </row>
-    <row r="650" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H650" s="3"/>
-      <c r="L650" s="3"/>
-    </row>
-    <row r="651" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H651" s="3"/>
-      <c r="L651" s="3"/>
-    </row>
-    <row r="652" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H652" s="3"/>
-      <c r="L652" s="3"/>
-    </row>
-    <row r="653" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H653" s="3"/>
-      <c r="L653" s="3"/>
-    </row>
-    <row r="654" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H654" s="3"/>
-      <c r="L654" s="3"/>
-    </row>
-    <row r="655" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H655" s="3"/>
-      <c r="L655" s="3"/>
-    </row>
-    <row r="656" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H656" s="3"/>
-      <c r="L656" s="3"/>
-    </row>
-    <row r="657" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H657" s="3"/>
-      <c r="L657" s="3"/>
-    </row>
-    <row r="658" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H658" s="3"/>
-      <c r="L658" s="3"/>
-    </row>
-    <row r="659" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H659" s="3"/>
-      <c r="L659" s="3"/>
-    </row>
-    <row r="660" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H660" s="3"/>
-      <c r="L660" s="3"/>
-    </row>
-    <row r="661" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H661" s="3"/>
-      <c r="L661" s="3"/>
-    </row>
-    <row r="662" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H662" s="3"/>
-      <c r="L662" s="3"/>
-    </row>
-    <row r="663" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H663" s="3"/>
-      <c r="L663" s="3"/>
-    </row>
-    <row r="664" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H664" s="3"/>
-      <c r="L664" s="3"/>
-    </row>
-    <row r="665" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H665" s="3"/>
-      <c r="L665" s="3"/>
-    </row>
-    <row r="666" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H666" s="3"/>
-      <c r="L666" s="3"/>
-    </row>
-    <row r="667" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H667" s="3"/>
-      <c r="L667" s="3"/>
-    </row>
-    <row r="668" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H668" s="3"/>
-      <c r="L668" s="3"/>
-    </row>
-    <row r="669" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H669" s="3"/>
-      <c r="L669" s="3"/>
-    </row>
-    <row r="670" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H670" s="3"/>
-      <c r="L670" s="3"/>
-    </row>
-    <row r="671" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H671" s="3"/>
-      <c r="L671" s="3"/>
-    </row>
-    <row r="672" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H672" s="3"/>
-      <c r="L672" s="3"/>
-    </row>
-    <row r="673" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H673" s="3"/>
-      <c r="L673" s="3"/>
-    </row>
-    <row r="674" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H674" s="3"/>
-      <c r="L674" s="3"/>
-    </row>
-    <row r="675" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H675" s="3"/>
-      <c r="L675" s="3"/>
-    </row>
-    <row r="676" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H676" s="3"/>
-      <c r="L676" s="3"/>
-    </row>
-    <row r="677" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H677" s="3"/>
-      <c r="L677" s="3"/>
-    </row>
-    <row r="678" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H678" s="3"/>
-      <c r="L678" s="3"/>
-    </row>
-    <row r="679" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H679" s="3"/>
-      <c r="L679" s="3"/>
-    </row>
-    <row r="680" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H680" s="3"/>
-      <c r="L680" s="3"/>
-    </row>
-    <row r="681" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H681" s="3"/>
-      <c r="L681" s="3"/>
-    </row>
-    <row r="682" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H682" s="3"/>
-      <c r="L682" s="3"/>
-    </row>
-    <row r="683" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H683" s="3"/>
-      <c r="L683" s="3"/>
-    </row>
-    <row r="684" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H684" s="3"/>
-      <c r="L684" s="3"/>
-    </row>
-    <row r="685" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H685" s="3"/>
-      <c r="L685" s="3"/>
-    </row>
-    <row r="686" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H686" s="3"/>
-      <c r="L686" s="3"/>
-    </row>
-    <row r="687" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H687" s="3"/>
-      <c r="L687" s="3"/>
-    </row>
-    <row r="688" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H688" s="3"/>
-      <c r="L688" s="3"/>
-    </row>
-    <row r="689" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H689" s="3"/>
-      <c r="L689" s="3"/>
-    </row>
-    <row r="690" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H690" s="3"/>
-      <c r="L690" s="3"/>
-    </row>
-    <row r="691" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H691" s="3"/>
-      <c r="L691" s="3"/>
-    </row>
-    <row r="692" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H692" s="3"/>
-      <c r="L692" s="3"/>
-    </row>
-    <row r="693" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H693" s="3"/>
-      <c r="L693" s="3"/>
-    </row>
-    <row r="694" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H694" s="3"/>
-      <c r="L694" s="3"/>
-    </row>
-    <row r="695" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H695" s="3"/>
-      <c r="L695" s="3"/>
-    </row>
-    <row r="696" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H696" s="3"/>
-      <c r="L696" s="3"/>
-    </row>
-    <row r="697" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H697" s="3"/>
-      <c r="L697" s="3"/>
-    </row>
-    <row r="698" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H698" s="3"/>
-      <c r="L698" s="3"/>
-    </row>
-    <row r="699" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H699" s="3"/>
-      <c r="L699" s="3"/>
-    </row>
-    <row r="700" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H700" s="3"/>
-      <c r="L700" s="3"/>
-    </row>
-    <row r="701" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H701" s="3"/>
-      <c r="L701" s="3"/>
-    </row>
-    <row r="702" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H702" s="3"/>
-      <c r="L702" s="3"/>
-    </row>
-    <row r="703" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H703" s="3"/>
-      <c r="L703" s="3"/>
-    </row>
-    <row r="704" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H704" s="3"/>
-      <c r="L704" s="3"/>
-    </row>
-    <row r="705" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H705" s="3"/>
-      <c r="L705" s="3"/>
-    </row>
-    <row r="706" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H706" s="3"/>
-      <c r="L706" s="3"/>
-    </row>
-    <row r="707" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H707" s="3"/>
-      <c r="L707" s="3"/>
-    </row>
-    <row r="708" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H708" s="3"/>
-      <c r="L708" s="3"/>
-    </row>
-    <row r="709" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H709" s="3"/>
-      <c r="L709" s="3"/>
-    </row>
-    <row r="710" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H710" s="3"/>
-      <c r="L710" s="3"/>
-    </row>
-    <row r="711" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H711" s="3"/>
-      <c r="L711" s="3"/>
-    </row>
-    <row r="712" spans="8:12" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H712" s="3"/>
-      <c r="L712" s="3"/>
-    </row>
+    <row r="98" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="99" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="100" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="101" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="102" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="103" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="104" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="105" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="106" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="107" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="108" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="109" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="110" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="111" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="112" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="113" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="114" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="115" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="116" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="117" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="118" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="119" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="120" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="121" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="122" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="123" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="124" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="125" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="126" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="127" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="128" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="129" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="130" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="131" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="132" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="133" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="134" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="135" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="136" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="137" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="138" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="139" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="140" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="141" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="142" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="143" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="144" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="145" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="146" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="147" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="148" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="149" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="150" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="151" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="152" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="153" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="154" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="155" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="156" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="157" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="158" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="159" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="160" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="161" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="162" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="163" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="164" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="165" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="166" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="167" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="168" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="169" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="170" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="171" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="172" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="173" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="174" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="175" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="176" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="177" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="178" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="179" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="180" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="181" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="182" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="183" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="184" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="185" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="186" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="187" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="188" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="189" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="190" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="191" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="192" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="193" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="194" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="195" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="196" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="197" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="198" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="199" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="200" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="201" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="202" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="203" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="204" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="205" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="206" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="207" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="208" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="209" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="210" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="211" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="212" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="213" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="214" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="215" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="216" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="217" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="218" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="219" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="220" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="221" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="222" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="223" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="224" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="225" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="226" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="227" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="228" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="229" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="230" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="231" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="232" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="233" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="234" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="235" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="236" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="237" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="238" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="239" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="240" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="241" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="242" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="243" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="244" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="245" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="246" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="247" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="248" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="249" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="250" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="251" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="252" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="253" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="254" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="255" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="256" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="257" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="258" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="259" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="260" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="261" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="262" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="263" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="264" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="265" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="266" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="267" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="268" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="269" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="270" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="271" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="272" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="273" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="274" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="275" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="276" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="277" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="278" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="279" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="280" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="281" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="282" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="283" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="284" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="285" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="286" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="287" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="288" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="289" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="290" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="291" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="292" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="293" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="294" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="295" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="296" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="297" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="298" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="299" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="300" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="301" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="302" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="303" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="304" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="305" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="306" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="307" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="308" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="309" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="310" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="311" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="312" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="313" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="314" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="315" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="316" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="317" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="318" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="319" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="320" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="321" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="322" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="323" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="324" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="325" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="326" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="327" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="328" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="329" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="330" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="331" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="332" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="333" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="334" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="335" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="336" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="337" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="338" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="339" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="340" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="341" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="342" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="343" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="344" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="345" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="346" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="347" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="348" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="349" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="350" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="351" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="352" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="353" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="354" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="355" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="356" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="357" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="358" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="359" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="360" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="361" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="362" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="363" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="364" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="365" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="366" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="367" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="368" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="369" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="370" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="371" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="372" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="373" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="374" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="375" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="376" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="377" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="378" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="379" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="380" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="381" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="382" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="383" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="384" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="385" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="386" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="387" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="388" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="389" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="390" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="391" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="392" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="393" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="394" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="395" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0" footer="0"/>
